--- a/schedule/Daily_Study_Schedule_3-5h.xlsx
+++ b/schedule/Daily_Study_Schedule_3-5h.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Exam Dates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Plan'!$A$1:$L$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Plan'!$A$1:$L$291</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -534,7 +533,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Study Guide column points to study-guides/*.md; Lab column is your lab environment; lab/lab.sh runs every lab.</t>
+          <t>Study Guide column points to prep/content/*.md; Lab column is your lab environment; prep/lab/lab.sh runs every lab.</t>
         </is>
       </c>
     </row>
@@ -563,6 +562,13 @@
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Deload: if you feel burned out, take one 2-hour day per fortnight (still do the recall block). Consistency beats intensity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Golden Kubestronaut track (G1-G9) appended after the core path: 2027-04-13 to 2027-07-14. Verify on cncf.io which certs currently count toward Golden Kubestronaut before booking.</t>
         </is>
       </c>
     </row>
@@ -577,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -688,7 +694,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>study-guides/01-git-github.md</t>
+          <t>content/01-git-github.md</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -736,7 +742,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>study-guides/01-git-github.md</t>
+          <t>content/01-git-github.md</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -786,7 +792,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>study-guides/01-git-github.md</t>
+          <t>content/01-git-github.md</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -838,7 +844,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -886,7 +892,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -938,7 +944,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -986,7 +992,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1036,7 +1042,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1088,7 +1094,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1136,7 +1142,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1188,7 +1194,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1236,7 +1242,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1286,7 +1292,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>study-guides/02-linux-fundamentals.md</t>
+          <t>content/02-linux-fundamentals.md</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1338,7 +1344,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -1386,7 +1392,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1436,7 +1442,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1488,7 +1494,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1536,7 +1542,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1588,7 +1594,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1636,7 +1642,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1684,7 +1690,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>study-guides/03-networking.md</t>
+          <t>content/03-networking.md</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -1736,7 +1742,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1784,7 +1790,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -1834,7 +1840,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -1886,7 +1892,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1934,7 +1940,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -1986,7 +1992,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2034,7 +2040,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -2084,7 +2090,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2136,7 +2142,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -2184,7 +2190,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2234,7 +2240,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>study-guides/04-rhcsa-ex200.md</t>
+          <t>content/04-rhcsa-ex200.md</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2286,7 +2292,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2336,7 +2342,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2388,7 +2394,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -2436,7 +2442,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -2486,7 +2492,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -2538,7 +2544,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -2586,7 +2592,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -2638,7 +2644,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -2686,7 +2692,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -2734,7 +2740,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>study-guides/05-rhce-ansible-ex294.md</t>
+          <t>content/05-rhce-ansible-ex294.md</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -2786,7 +2792,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -2834,7 +2840,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -2884,7 +2890,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -2936,7 +2942,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -2984,7 +2990,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -3036,7 +3042,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -3084,7 +3090,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
@@ -3134,7 +3140,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -3186,7 +3192,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -3234,7 +3240,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -3284,7 +3290,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>study-guides/06-docker.md</t>
+          <t>content/06-docker.md</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -3336,7 +3342,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>study-guides/07-cicd-github-actions.md</t>
+          <t>content/07-cicd-github-actions.md</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -3386,7 +3392,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>study-guides/07-cicd-github-actions.md</t>
+          <t>content/07-cicd-github-actions.md</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -3438,7 +3444,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>study-guides/07-cicd-github-actions.md</t>
+          <t>content/07-cicd-github-actions.md</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
@@ -3486,7 +3492,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>study-guides/07-cicd-github-actions.md</t>
+          <t>content/07-cicd-github-actions.md</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -3534,7 +3540,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>study-guides/07-cicd-github-actions.md</t>
+          <t>content/07-cicd-github-actions.md</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -3586,7 +3592,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -3634,7 +3640,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -3684,7 +3690,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -3736,7 +3742,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -3784,7 +3790,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -3836,7 +3842,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -3884,7 +3890,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -3934,7 +3940,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>study-guides/08-kubernetes-kcna.md</t>
+          <t>content/08-kubernetes-kcna.md</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -3986,7 +3992,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -4034,7 +4040,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -4086,7 +4092,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -4134,7 +4140,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -4184,7 +4190,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -4236,7 +4242,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -4284,7 +4290,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -4334,7 +4340,7 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -4386,7 +4392,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -4434,7 +4440,7 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -4482,7 +4488,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>study-guides/09-cka.md</t>
+          <t>content/09-cka.md</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
@@ -4534,7 +4540,7 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -4582,7 +4588,7 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -4632,7 +4638,7 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -4684,7 +4690,7 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -4732,7 +4738,7 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
@@ -4784,7 +4790,7 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -4832,7 +4838,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
@@ -4880,7 +4886,7 @@
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>study-guides/(CKAD guide pending) + 09-cka.md</t>
+          <t>content/10-ckad.md</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -4932,7 +4938,7 @@
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
@@ -4980,7 +4986,7 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -5030,7 +5036,7 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
@@ -5082,7 +5088,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -5130,7 +5136,7 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
@@ -5184,7 +5190,7 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
@@ -5232,7 +5238,7 @@
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
@@ -5280,7 +5286,7 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
@@ -5328,7 +5334,7 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>study-guides/11-aws-devops.md</t>
+          <t>content/11-aws-devops.md</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
@@ -5380,7 +5386,7 @@
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
@@ -5428,7 +5434,7 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
@@ -5482,7 +5488,7 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
@@ -5530,7 +5536,7 @@
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
@@ -5578,7 +5584,7 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
@@ -5628,7 +5634,7 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -5680,7 +5686,7 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -5728,7 +5734,7 @@
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
@@ -5780,7 +5786,7 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
@@ -5828,7 +5834,7 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -5876,7 +5882,7 @@
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I106" s="8" t="inlineStr">
@@ -5928,7 +5934,7 @@
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -5976,7 +5982,7 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -6024,7 +6030,7 @@
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -6076,7 +6082,7 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -6124,7 +6130,7 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
@@ -6172,7 +6178,7 @@
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>study-guides/12-openshift-do188-do280.md</t>
+          <t>content/12-openshift-do188-do280.md</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
@@ -6226,7 +6232,7 @@
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">
@@ -6274,7 +6280,7 @@
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
@@ -6322,7 +6328,7 @@
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
@@ -6372,7 +6378,7 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
@@ -6424,7 +6430,7 @@
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
@@ -6472,7 +6478,7 @@
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
@@ -6526,7 +6532,7 @@
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -6574,7 +6580,7 @@
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr">
@@ -6622,7 +6628,7 @@
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -6670,7 +6676,7 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>study-guides/13-openshift-do380.md</t>
+          <t>content/13-openshift-do380.md</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -6722,7 +6728,7 @@
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -6770,7 +6776,7 @@
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -6820,7 +6826,7 @@
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -6872,7 +6878,7 @@
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -6920,7 +6926,7 @@
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -6972,7 +6978,7 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
@@ -7020,7 +7026,7 @@
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
@@ -7068,7 +7074,7 @@
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
@@ -7120,7 +7126,7 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
@@ -7168,7 +7174,7 @@
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
@@ -7218,7 +7224,7 @@
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -7270,7 +7276,7 @@
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
@@ -7318,7 +7324,7 @@
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
@@ -7366,7 +7372,7 @@
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -7418,7 +7424,7 @@
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
@@ -7466,7 +7472,7 @@
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
@@ -7514,7 +7520,7 @@
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>study-guides/14-15-kcsa-cks.md</t>
+          <t>content/14-15-kcsa-cks.md</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
@@ -7568,7 +7574,7 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>study-guides/16-rhacs-do430.md</t>
+          <t>content/16-rhacs-do430.md</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
@@ -7616,7 +7622,7 @@
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>study-guides/16-rhacs-do430.md</t>
+          <t>content/16-rhacs-do430.md</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
@@ -7664,7 +7670,7 @@
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>study-guides/16-rhacs-do430.md</t>
+          <t>content/16-rhacs-do430.md</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
@@ -7716,7 +7722,7 @@
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>study-guides/16-rhacs-do430.md</t>
+          <t>content/16-rhacs-do430.md</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
@@ -7764,7 +7770,7 @@
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>study-guides/16-rhacs-do430.md</t>
+          <t>content/16-rhacs-do430.md</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
@@ -7812,7 +7818,7 @@
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>study-guides/16-rhacs-do430.md</t>
+          <t>content/16-rhacs-do430.md</t>
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr">
@@ -7862,7 +7868,7 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>study-guides/16-rhacs-do430.md</t>
+          <t>content/16-rhacs-do430.md</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
@@ -7914,7 +7920,7 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>study-guides/17-argo-capa.md</t>
+          <t>content/17-argo-capa.md</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
@@ -7962,7 +7968,7 @@
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>study-guides/17-argo-capa.md</t>
+          <t>content/17-argo-capa.md</t>
         </is>
       </c>
       <c r="I148" s="8" t="inlineStr">
@@ -8014,7 +8020,7 @@
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>study-guides/17-argo-capa.md</t>
+          <t>content/17-argo-capa.md</t>
         </is>
       </c>
       <c r="I149" s="5" t="inlineStr">
@@ -8062,7 +8068,7 @@
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>study-guides/17-argo-capa.md</t>
+          <t>content/17-argo-capa.md</t>
         </is>
       </c>
       <c r="I150" s="5" t="inlineStr">
@@ -8112,7 +8118,7 @@
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>study-guides/17-argo-capa.md</t>
+          <t>content/17-argo-capa.md</t>
         </is>
       </c>
       <c r="I151" s="5" t="inlineStr">
@@ -8164,7 +8170,7 @@
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>study-guides/17-argo-capa.md</t>
+          <t>content/17-argo-capa.md</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
@@ -8212,7 +8218,7 @@
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>study-guides/17-argo-capa.md</t>
+          <t>content/17-argo-capa.md</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
@@ -8266,7 +8272,7 @@
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -8314,7 +8320,7 @@
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I155" s="8" t="inlineStr">
@@ -8362,7 +8368,7 @@
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -8414,7 +8420,7 @@
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
@@ -8462,7 +8468,7 @@
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
@@ -8512,7 +8518,7 @@
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
@@ -8564,7 +8570,7 @@
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
@@ -8612,7 +8618,7 @@
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>study-guides/18-istio-ica.md</t>
+          <t>content/18-istio-ica.md</t>
         </is>
       </c>
       <c r="I161" s="5" t="inlineStr">
@@ -8666,7 +8672,7 @@
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I162" s="8" t="inlineStr">
@@ -8714,7 +8720,7 @@
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I163" s="5" t="inlineStr">
@@ -8762,7 +8768,7 @@
       </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I164" s="5" t="inlineStr">
@@ -8814,7 +8820,7 @@
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I165" s="5" t="inlineStr">
@@ -8862,7 +8868,7 @@
       </c>
       <c r="H166" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I166" s="5" t="inlineStr">
@@ -8910,7 +8916,7 @@
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I167" s="5" t="inlineStr">
@@ -8962,7 +8968,7 @@
       </c>
       <c r="H168" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I168" s="5" t="inlineStr">
@@ -9010,7 +9016,7 @@
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
@@ -9058,7 +9064,7 @@
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
@@ -9110,7 +9116,7 @@
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
@@ -9158,7 +9164,7 @@
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I172" s="5" t="inlineStr">
@@ -9206,7 +9212,7 @@
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I173" s="5" t="inlineStr">
@@ -9258,7 +9264,7 @@
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
@@ -9306,7 +9312,7 @@
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I175" s="5" t="inlineStr">
@@ -9360,7 +9366,7 @@
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
@@ -9408,7 +9414,7 @@
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
@@ -9456,7 +9462,7 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
@@ -9508,7 +9514,7 @@
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
@@ -9556,7 +9562,7 @@
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
@@ -9604,7 +9610,7 @@
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
@@ -9656,7 +9662,7 @@
       </c>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
@@ -9704,7 +9710,7 @@
       </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I183" s="8" t="inlineStr">
@@ -9754,7 +9760,7 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>study-guides/19-ai-llm-security.md</t>
+          <t>content/19-ai-llm-security.md</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
@@ -9806,7 +9812,7 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
@@ -9854,7 +9860,7 @@
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
@@ -9904,7 +9910,7 @@
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
@@ -9956,7 +9962,7 @@
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
@@ -10004,7 +10010,7 @@
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
@@ -10052,7 +10058,7 @@
       </c>
       <c r="H190" s="8" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I190" s="8" t="inlineStr">
@@ -10102,7 +10108,7 @@
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I191" s="5" t="inlineStr">
@@ -10154,7 +10160,7 @@
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I192" s="5" t="inlineStr">
@@ -10202,7 +10208,7 @@
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
@@ -10250,7 +10256,7 @@
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
@@ -10302,7 +10308,7 @@
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
@@ -10350,7 +10356,7 @@
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I196" s="5" t="inlineStr">
@@ -10398,7 +10404,7 @@
       </c>
       <c r="H197" s="8" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I197" s="8" t="inlineStr">
@@ -10446,7 +10452,7 @@
       </c>
       <c r="H198" s="5" t="inlineStr">
         <is>
-          <t>study-guides/20-capstone-portfolio.md</t>
+          <t>content/20-capstone-portfolio.md</t>
         </is>
       </c>
       <c r="I198" s="5" t="inlineStr">
@@ -10466,10 +10472,4696 @@
       </c>
       <c r="L198" s="5" t="inlineStr"/>
     </row>
+    <row r="199">
+      <c r="A199" s="14" t="n">
+        <v>46490</v>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>Ubuntu vs RHEL: apt/dpkg, netplan, ufw, AppArmor</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="n"/>
+      <c r="K199" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="14" t="n">
+        <v>46491</v>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>Users, groups, sudo, SSH hardening</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="n"/>
+      <c r="K200" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="14" t="n">
+        <v>46492</v>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>Storage: LVM, mdadm RAID, swap, quotas</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J201" s="6" t="n"/>
+      <c r="K201" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="14" t="n">
+        <v>46493</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>NFS server/client, autofs</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="n"/>
+      <c r="K202" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="14" t="n">
+        <v>46494</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>Networking: netplan bonding/bridging, systemd-resolved</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="n"/>
+      <c r="K203" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="14" t="n">
+        <v>46495</v>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: LFCS</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="n"/>
+      <c r="K204" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="14" t="n">
+        <v>46496</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>iptables/nftables NAT + port forwarding</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="n"/>
+      <c r="K205" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="14" t="n">
+        <v>46497</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>nginx/HAProxy reverse proxy and load balancing</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="n"/>
+      <c r="K206" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="14" t="n">
+        <v>46498</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="n"/>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="14" t="n">
+        <v>46499</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>Sit LFCS (or final mock if not booked)</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>content/29-lfcs.md</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/lfcs (2 Ubuntu 24.04 VMs)</t>
+        </is>
+      </c>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: LFCS - Linux Foundation Certified System Administrator; DELIVERABLE: LFCS task log: 30 tasks solved on Ubuntu VMs</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="14" t="n">
+        <v>46500</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>Prometheus architecture, data model, labels</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I209" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="n"/>
+      <c r="K209" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="14" t="n">
+        <v>46501</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>Scrape configs, service discovery, relabelling</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J210" s="6" t="n"/>
+      <c r="K210" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="14" t="n">
+        <v>46502</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: PCA</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="n"/>
+      <c r="K211" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="14" t="n">
+        <v>46503</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>PromQL: selectors, rate/irate/increase</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I212" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J212" s="6" t="n"/>
+      <c r="K212" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="14" t="n">
+        <v>46504</v>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>PromQL: aggregation, joins, histogram_quantile, subqueries</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I213" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J213" s="6" t="n"/>
+      <c r="K213" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="14" t="n">
+        <v>46505</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>Recording rules and alerting rules</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J214" s="6" t="n"/>
+      <c r="K214" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="14" t="n">
+        <v>46506</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>Alertmanager routing, grouping, inhibition, silences</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J215" s="6" t="n"/>
+      <c r="K215" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="14" t="n">
+        <v>46507</v>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>Exporters: node, blackbox; instrumentation client libs</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I216" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J216" s="6" t="n"/>
+      <c r="K216" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="14" t="n">
+        <v>46508</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>Grafana dashboards, federation, remote write</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I217" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J217" s="6" t="n"/>
+      <c r="K217" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="14" t="n">
+        <v>46509</v>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: PCA</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J218" s="6" t="n"/>
+      <c r="K218" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="14" t="n">
+        <v>46510</v>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>Prometheus architecture, data model, labels</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J219" s="6" t="n"/>
+      <c r="K219" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="14" t="n">
+        <v>46511</v>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>Scrape configs, service discovery, relabelling</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I220" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J220" s="6" t="n"/>
+      <c r="K220" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="14" t="n">
+        <v>46512</v>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I221" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J221" s="6" t="n"/>
+      <c r="K221" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="14" t="n">
+        <v>46513</v>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>Sit PCA (or final mock if not booked)</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>content/22-pca-prometheus.md</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/pca (namespace prom-lab)</t>
+        </is>
+      </c>
+      <c r="J222" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: PCA - Prometheus Certified Associate; DELIVERABLE: PromQL exercise set + alert rules repo</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="14" t="n">
+        <v>46514</v>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>Signals: traces, metrics, logs; API vs SDK</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J223" s="6" t="n"/>
+      <c r="K223" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="14" t="n">
+        <v>46515</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Context propagation, semantic conventions</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J224" s="6" t="n"/>
+      <c r="K224" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="14" t="n">
+        <v>46516</v>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: OTCA</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I225" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J225" s="6" t="n"/>
+      <c r="K225" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="14" t="n">
+        <v>46517</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>Collector: receivers, processors, exporters, pipelines</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J226" s="6" t="n"/>
+      <c r="K226" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="14" t="n">
+        <v>46518</v>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>Sampling strategies, OTLP</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J227" s="6" t="n"/>
+      <c r="K227" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="14" t="n">
+        <v>46519</v>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="inlineStr">
+        <is>
+          <t>Auto-instrumentation + OTel Operator</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J228" s="6" t="n"/>
+      <c r="K228" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="14" t="n">
+        <v>46520</v>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>Backends: Jaeger + Prometheus; debugging pipelines</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I229" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J229" s="6" t="n"/>
+      <c r="K229" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="14" t="n">
+        <v>46521</v>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>Signals: traces, metrics, logs; API vs SDK</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J230" s="6" t="n"/>
+      <c r="K230" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="14" t="n">
+        <v>46522</v>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J231" s="6" t="n"/>
+      <c r="K231" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="14" t="n">
+        <v>46523</v>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: OTCA</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="inlineStr">
+        <is>
+          <t>content/23-otca-opentelemetry.md</t>
+        </is>
+      </c>
+      <c r="I232" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/observability/otel (namespace otel-lab)</t>
+        </is>
+      </c>
+      <c r="J232" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: OTCA - OpenTelemetry Certified Associate; DELIVERABLE: Instrumented demo app with traces in Jaeger</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="14" t="n">
+        <v>46524</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>eBPF basics, Cilium architecture, identity</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J233" s="6" t="n"/>
+      <c r="K233" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="14" t="n">
+        <v>46525</v>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>Install + cilium CLI, IPAM, kube-proxy replacement</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I234" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J234" s="6" t="n"/>
+      <c r="K234" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="14" t="n">
+        <v>46526</v>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>CiliumNetworkPolicy L3/L4</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J235" s="6" t="n"/>
+      <c r="K235" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="14" t="n">
+        <v>46527</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>L7 HTTP and DNS/FQDN policies</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I236" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J236" s="6" t="n"/>
+      <c r="K236" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="14" t="n">
+        <v>46528</v>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>Hubble: flows, UI, troubleshooting</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J237" s="6" t="n"/>
+      <c r="K237" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="14" t="n">
+        <v>46529</v>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>Cluster mesh, Gateway API, service mesh</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I238" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J238" s="6" t="n"/>
+      <c r="K238" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="14" t="n">
+        <v>46530</v>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: CCA</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I239" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J239" s="6" t="n"/>
+      <c r="K239" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="14" t="n">
+        <v>46531</v>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>BGP, LB-IPAM, WireGuard/IPsec encryption</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H240" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I240" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J240" s="6" t="n"/>
+      <c r="K240" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="14" t="n">
+        <v>46532</v>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>eBPF basics, Cilium architecture, identity</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I241" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J241" s="6" t="n"/>
+      <c r="K241" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="14" t="n">
+        <v>46533</v>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>Install + cilium CLI, IPAM, kube-proxy replacement</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H242" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J242" s="6" t="n"/>
+      <c r="K242" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="14" t="n">
+        <v>46534</v>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>CiliumNetworkPolicy L3/L4</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I243" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J243" s="6" t="n"/>
+      <c r="K243" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="14" t="n">
+        <v>46535</v>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>L7 HTTP and DNS/FQDN policies</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I244" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J244" s="6" t="n"/>
+      <c r="K244" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="14" t="n">
+        <v>46536</v>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G245" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I245" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J245" s="6" t="n"/>
+      <c r="K245" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="14" t="n">
+        <v>46537</v>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: CCA</t>
+        </is>
+      </c>
+      <c r="G246" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H246" s="5" t="inlineStr">
+        <is>
+          <t>content/24-cca-cilium.md</t>
+        </is>
+      </c>
+      <c r="I246" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/cilium (namespace cilium-lab), ./lab.sh kind up cilium</t>
+        </is>
+      </c>
+      <c r="J246" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: CCA - Cilium Certified Associate; DELIVERABLE: Cilium policy pack + Hubble flow write-up</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="14" t="n">
+        <v>46538</v>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>Kyverno architecture, admission webhooks</t>
+        </is>
+      </c>
+      <c r="G247" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I247" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J247" s="6" t="n"/>
+      <c r="K247" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="14" t="n">
+        <v>46539</v>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>Validate policies, match/exclude, preconditions, JMESPath</t>
+        </is>
+      </c>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I248" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J248" s="6" t="n"/>
+      <c r="K248" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="14" t="n">
+        <v>46540</v>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>Mutate + generate policies</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I249" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J249" s="6" t="n"/>
+      <c r="K249" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="14" t="n">
+        <v>46541</v>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>verifyImages, cleanup policies, exceptions</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I250" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J250" s="6" t="n"/>
+      <c r="K250" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="14" t="n">
+        <v>46542</v>
+      </c>
+      <c r="B251" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>PolicyReports, audit vs enforce</t>
+        </is>
+      </c>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I251" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J251" s="6" t="n"/>
+      <c r="K251" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="14" t="n">
+        <v>46543</v>
+      </c>
+      <c r="B252" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="inlineStr">
+        <is>
+          <t>kyverno CLI apply/test, Pod Security library</t>
+        </is>
+      </c>
+      <c r="G252" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I252" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J252" s="6" t="n"/>
+      <c r="K252" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="14" t="n">
+        <v>46544</v>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: KCA</t>
+        </is>
+      </c>
+      <c r="G253" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H253" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I253" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J253" s="6" t="n"/>
+      <c r="K253" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="14" t="n">
+        <v>46545</v>
+      </c>
+      <c r="B254" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="inlineStr">
+        <is>
+          <t>Kyverno architecture, admission webhooks</t>
+        </is>
+      </c>
+      <c r="G254" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H254" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I254" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J254" s="6" t="n"/>
+      <c r="K254" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="14" t="n">
+        <v>46546</v>
+      </c>
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I255" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J255" s="6" t="n"/>
+      <c r="K255" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="14" t="n">
+        <v>46547</v>
+      </c>
+      <c r="B256" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="inlineStr">
+        <is>
+          <t>Sit KCA (or final mock if not booked)</t>
+        </is>
+      </c>
+      <c r="G256" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="inlineStr">
+        <is>
+          <t>content/25-kca-kyverno.md</t>
+        </is>
+      </c>
+      <c r="I256" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/kyverno (namespace kyverno-lab)</t>
+        </is>
+      </c>
+      <c r="J256" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: KCA - Kyverno Certified Associate; DELIVERABLE: Kyverno policy library with passing kyverno test</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="14" t="n">
+        <v>46548</v>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>OpenGitOps principles and terminology</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="inlineStr">
+        <is>
+          <t>content/26-cgoa-gitops.md</t>
+        </is>
+      </c>
+      <c r="I257" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/flux (namespace flux-lab)</t>
+        </is>
+      </c>
+      <c r="J257" s="6" t="n"/>
+      <c r="K257" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="14" t="n">
+        <v>46549</v>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>Patterns: pull vs push, app-of-apps, promotion, drift</t>
+        </is>
+      </c>
+      <c r="G258" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H258" s="5" t="inlineStr">
+        <is>
+          <t>content/26-cgoa-gitops.md</t>
+        </is>
+      </c>
+      <c r="I258" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/flux (namespace flux-lab)</t>
+        </is>
+      </c>
+      <c r="J258" s="6" t="n"/>
+      <c r="K258" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="14" t="n">
+        <v>46550</v>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="inlineStr">
+        <is>
+          <t>Flux: bootstrap, GitRepository, Kustomization, HelmRelease</t>
+        </is>
+      </c>
+      <c r="G259" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="inlineStr">
+        <is>
+          <t>content/26-cgoa-gitops.md</t>
+        </is>
+      </c>
+      <c r="I259" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/flux (namespace flux-lab)</t>
+        </is>
+      </c>
+      <c r="J259" s="6" t="n"/>
+      <c r="K259" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="14" t="n">
+        <v>46551</v>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: CGOA</t>
+        </is>
+      </c>
+      <c r="G260" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H260" s="5" t="inlineStr">
+        <is>
+          <t>content/26-cgoa-gitops.md</t>
+        </is>
+      </c>
+      <c r="I260" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/flux (namespace flux-lab)</t>
+        </is>
+      </c>
+      <c r="J260" s="6" t="n"/>
+      <c r="K260" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="14" t="n">
+        <v>46552</v>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>Flux image automation; Flux vs Argo CD</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H261" s="5" t="inlineStr">
+        <is>
+          <t>content/26-cgoa-gitops.md</t>
+        </is>
+      </c>
+      <c r="I261" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/flux (namespace flux-lab)</t>
+        </is>
+      </c>
+      <c r="J261" s="6" t="n"/>
+      <c r="K261" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="14" t="n">
+        <v>46553</v>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H262" s="5" t="inlineStr">
+        <is>
+          <t>content/26-cgoa-gitops.md</t>
+        </is>
+      </c>
+      <c r="I262" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/flux (namespace flux-lab)</t>
+        </is>
+      </c>
+      <c r="J262" s="6" t="n"/>
+      <c r="K262" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="14" t="n">
+        <v>46554</v>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Sit CGOA (or final mock if not booked)</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H263" s="5" t="inlineStr">
+        <is>
+          <t>content/26-cgoa-gitops.md</t>
+        </is>
+      </c>
+      <c r="I263" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/flux (namespace flux-lab)</t>
+        </is>
+      </c>
+      <c r="J263" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: CGOA - Certified GitOps Associate; DELIVERABLE: Flux-managed podinfo with env promotion</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="14" t="n">
+        <v>46555</v>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>Backstage architecture: frontend, backend, plugins</t>
+        </is>
+      </c>
+      <c r="G264" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H264" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I264" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J264" s="6" t="n"/>
+      <c r="K264" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="14" t="n">
+        <v>46556</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Software catalog, entity kinds, catalog-info.yaml</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I265" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J265" s="6" t="n"/>
+      <c r="K265" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="14" t="n">
+        <v>46557</v>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>Software templates (scaffolder)</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H266" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I266" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J266" s="6" t="n"/>
+      <c r="K266" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="14" t="n">
+        <v>46558</v>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: CBA</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I267" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J267" s="6" t="n"/>
+      <c r="K267" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="14" t="n">
+        <v>46559</v>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>TechDocs</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H268" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I268" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J268" s="6" t="n"/>
+      <c r="K268" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="14" t="n">
+        <v>46560</v>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Auth, permissions, plugin development basics</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I269" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J269" s="6" t="n"/>
+      <c r="K269" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="14" t="n">
+        <v>46561</v>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>Backstage architecture: frontend, backend, plugins</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I270" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J270" s="6" t="n"/>
+      <c r="K270" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="14" t="n">
+        <v>46562</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Software catalog, entity kinds, catalog-info.yaml</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I271" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J271" s="6" t="n"/>
+      <c r="K271" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="14" t="n">
+        <v>46563</v>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I272" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J272" s="6" t="n"/>
+      <c r="K272" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="14" t="n">
+        <v>46564</v>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Sit CBA (or final mock if not booked)</t>
+        </is>
+      </c>
+      <c r="G273" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>content/27-cba-backstage.md</t>
+        </is>
+      </c>
+      <c r="I273" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/backstage</t>
+        </is>
+      </c>
+      <c r="J273" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: CBA - Certified Backstage Associate; DELIVERABLE: Local Backstage with catalog + scaffolder template</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="14" t="n">
+        <v>46565</v>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: CNPA</t>
+        </is>
+      </c>
+      <c r="G274" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H274" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I274" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp (namespace platform-lab)</t>
+        </is>
+      </c>
+      <c r="J274" s="6" t="n"/>
+      <c r="K274" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="14" t="n">
+        <v>46566</v>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Platform as a product, IDPs, golden paths</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I275" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp (namespace platform-lab)</t>
+        </is>
+      </c>
+      <c r="J275" s="6" t="n"/>
+      <c r="K275" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="14" t="n">
+        <v>46567</v>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>Self-service: operators, Crossplane concepts</t>
+        </is>
+      </c>
+      <c r="G276" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I276" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp (namespace platform-lab)</t>
+        </is>
+      </c>
+      <c r="J276" s="6" t="n"/>
+      <c r="K276" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="14" t="n">
+        <v>46568</v>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>Policy as code, multi-tenancy</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H277" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I277" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp (namespace platform-lab)</t>
+        </is>
+      </c>
+      <c r="J277" s="6" t="n"/>
+      <c r="K277" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="14" t="n">
+        <v>46569</v>
+      </c>
+      <c r="B278" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>Platform observability, DORA/SPACE metrics</t>
+        </is>
+      </c>
+      <c r="G278" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I278" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp (namespace platform-lab)</t>
+        </is>
+      </c>
+      <c r="J278" s="6" t="n"/>
+      <c r="K278" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="14" t="n">
+        <v>46570</v>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I279" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp (namespace platform-lab)</t>
+        </is>
+      </c>
+      <c r="J279" s="6" t="n"/>
+      <c r="K279" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="14" t="n">
+        <v>46571</v>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>Sit CNPA (or final mock if not booked)</t>
+        </is>
+      </c>
+      <c r="G280" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H280" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I280" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp (namespace platform-lab)</t>
+        </is>
+      </c>
+      <c r="J280" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: CNPA - Cloud Native Platform Engineering Associate; DELIVERABLE: Namespace-as-a-service golden path</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="14" t="n">
+        <v>46572</v>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: CNPE</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I281" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J281" s="6" t="n"/>
+      <c r="K281" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="14" t="n">
+        <v>46573</v>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>Build the platform: namespace-as-a-service via Kustomize</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H282" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I282" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J282" s="6" t="n"/>
+      <c r="K282" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="14" t="n">
+        <v>46574</v>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>GitOps delivery of platform components</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I283" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J283" s="6" t="n"/>
+      <c r="K283" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="14" t="n">
+        <v>46575</v>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>Policy guardrails with Kyverno on the platform</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H284" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I284" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J284" s="6" t="n"/>
+      <c r="K284" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="14" t="n">
+        <v>46576</v>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>Observability for tenants (Prometheus + OTel)</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H285" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I285" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J285" s="6" t="n"/>
+      <c r="K285" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="14" t="n">
+        <v>46577</v>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="inlineStr">
+        <is>
+          <t>Composition / self-service API exercise</t>
+        </is>
+      </c>
+      <c r="G286" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I286" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J286" s="6" t="n"/>
+      <c r="K286" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="14" t="n">
+        <v>46578</v>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>End-to-end golden path demo</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 learn (1h) | 1:15 deep hands-on lab (2h30) | 3:45 build/commit deliverable to GitHub (1h) | 4:45 self-check (15m)</t>
+        </is>
+      </c>
+      <c r="H287" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I287" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J287" s="6" t="n"/>
+      <c r="K287" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="14" t="n">
+        <v>46579</v>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>Weekly review + timed practice: CNPE</t>
+        </is>
+      </c>
+      <c r="G288" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall quiz on the week (30m) | 0:30 timed practice / mock tasks (1h30) | 2:00 fix weak spots + update notes (45m) | 2:45 plan next week, update Status (15m)</t>
+        </is>
+      </c>
+      <c r="H288" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I288" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J288" s="6" t="n"/>
+      <c r="K288" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="14" t="n">
+        <v>46580</v>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>Build the platform: namespace-as-a-service via Kustomize</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall yesterday (15m) | 0:15 learn: guide + docs (1h) | 1:15 hands-on lab (2h) | 3:15 notes + commit (30m) | 3:45 self-check Qs (15m)</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I289" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J289" s="6" t="n"/>
+      <c r="K289" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="14" t="n">
+        <v>46581</v>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>Full timed mock exam</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H290" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I290" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J290" s="6" t="n"/>
+      <c r="K290" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="14" t="n">
+        <v>46582</v>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>Sit CNPE (or final mock if not booked)</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr">
+        <is>
+          <t>0:00 recall (15m) | 0:15 full timed mock or exam-style tasks (2h30) | 2:45 review every miss, redo it (1h) | 3:45 flashcards (15m)</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="inlineStr">
+        <is>
+          <t>content/28-cnpa-cnpe-platform.md</t>
+        </is>
+      </c>
+      <c r="I291" s="5" t="inlineStr">
+        <is>
+          <t>lab/golden/platform/idp + all Golden labs</t>
+        </is>
+      </c>
+      <c r="J291" s="6" t="inlineStr">
+        <is>
+          <t>EXAM: CNPE - Certified Cloud Native Platform Engineer; DELIVERABLE: Golden Kubestronaut platform demo repo</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="L291" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L198"/>
+  <autoFilter ref="A1:L291"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K198" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K291" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Done,Skipped,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10483,7 +15175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12778,6 +17470,294 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>G1. LFCS</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>46490</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>46499</v>
+      </c>
+      <c r="F72" s="16" t="n"/>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>LFCS - Linux Foundation Certified System Administrator</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>LFCS task log: 30 tasks solved on Ubuntu VMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>G2. PCA</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>46500</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>46513</v>
+      </c>
+      <c r="F73" s="16" t="n"/>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>PCA - Prometheus Certified Associate</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>PromQL exercise set + alert rules repo</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>G3. OTCA</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>46514</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>46523</v>
+      </c>
+      <c r="F74" s="16" t="n"/>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>OTCA - OpenTelemetry Certified Associate</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>Instrumented demo app with traces in Jaeger</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>G4. CCA</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>46524</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>46537</v>
+      </c>
+      <c r="F75" s="16" t="n"/>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>CCA - Cilium Certified Associate</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>Cilium policy pack + Hubble flow write-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>G5. KCA</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>46538</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>46547</v>
+      </c>
+      <c r="F76" s="16" t="n"/>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>KCA - Kyverno Certified Associate</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>Kyverno policy library with passing kyverno test</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>G6. CGOA</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D77" s="16" t="n">
+        <v>46548</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>46554</v>
+      </c>
+      <c r="F77" s="16" t="n"/>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>CGOA - Certified GitOps Associate</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>Flux-managed podinfo with env promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>G7. CBA</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>46555</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>46564</v>
+      </c>
+      <c r="F78" s="16" t="n"/>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>CBA - Certified Backstage Associate</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>Local Backstage with catalog + scaffolder template</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>G8. CNPA</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D79" s="16" t="n">
+        <v>46565</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>46571</v>
+      </c>
+      <c r="F79" s="16" t="n"/>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>CNPA - Cloud Native Platform Engineering Associate</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Namespace-as-a-service golden path</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>G9. CNPE</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>46572</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>46582</v>
+      </c>
+      <c r="F80" s="16" t="n"/>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>CNPE - Certified Cloud Native Platform Engineer</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>Golden Kubestronaut platform demo repo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12789,7 +17769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -13036,6 +18016,168 @@
         <v>46438</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LFCS - Linux Foundation Certified System Administrator</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>46499</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>46485</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PCA - Prometheus Certified Associate</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>46513</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>46499</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OTCA - OpenTelemetry Certified Associate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>46523</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>46509</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CCA - Cilium Certified Associate</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>46537</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>46523</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KCA - Kyverno Certified Associate</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>46547</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>46533</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CGOA - Certified GitOps Associate</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>46554</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>46540</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CBA - Certified Backstage Associate</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>46564</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CNPA - Cloud Native Platform Engineering Associate</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>46571</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>46557</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CNPE - Certified Cloud Native Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>46582</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>46568</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
